--- a/Active_FOC.xlsx
+++ b/Active_FOC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WhatsAppSender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AE2A73-0882-4780-A2BB-92B0DF2486FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5602E-F288-4636-90C6-221DF4284F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="11520" xr2:uid="{EFA97314-E11F-4967-9D7F-D66E1D560F7F}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="9" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -8713,6 +8713,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -30436,7 +30437,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{41D171BA-45C9-4C1A-BB37-C8F49792EA96}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{41D171BA-45C9-4C1A-BB37-C8F49792EA96}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="AC4:AI65" firstHeaderRow="1" firstDataRow="1" firstDataCol="7" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="24">
     <pivotField compact="0" outline="0" showAll="0"/>
